--- a/docs/Buch Camille Chronicles/Zeitlinie_Soulbound.xlsx
+++ b/docs/Buch Camille Chronicles/Zeitlinie_Soulbound.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julian Dauner\Documents\GitHub\pnpWiki\docs\Buch Camille Chronicles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B4AEB4-D3F2-473D-8096-B8FC5BA20C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0CBEB4-9613-4CB9-8793-A92097FA7FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5205" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Monat</t>
   </si>
@@ -81,6 +81,15 @@
     <t>Death of Bureaucratess Nalli 
 Camill going to Asarat's Peak
 Camill checks into the bar 'Ubir Ubar’</t>
+  </si>
+  <si>
+    <t>Irnatrav</t>
+  </si>
+  <si>
+    <t>Jevan's Birthday</t>
+  </si>
+  <si>
+    <t>War against Kekar'Om</t>
   </si>
 </sst>
 </file>
@@ -409,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="26.109375" bestFit="1" customWidth="1"/>
@@ -433,88 +442,110 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3735</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>3736</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>3739</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C2">
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
         <v>3761</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="C5">
+      <c r="C9">
         <v>52</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" t="s">
+    <row r="10" spans="1:5" ht="144" x14ac:dyDescent="0.3">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s">
         <v>5</v>
       </c>
-      <c r="C6">
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="C7">
+    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C8">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="C9">
+    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="C13">
         <v>18</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="C10">
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="C14">
         <v>19</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C11">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15">
         <v>20</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="C15">
+    <row r="19" spans="3:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="C19">
         <v>38</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
